--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,200 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128186215</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>406750</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6715629</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128186216</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>406821</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6715709</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>128186215</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128186216</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>128186215</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128186216</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>128186215</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128186216</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>128186215</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128186216</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>128186215</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>128186216</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104424814</v>
+        <v>104424296</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406962.1764483831</v>
+        <v>406779</v>
       </c>
       <c r="R2" t="n">
-        <v>6715888.726293258</v>
+        <v>6715766</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104424291</v>
+        <v>104424278</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406870.9485506968</v>
+        <v>406943</v>
       </c>
       <c r="R3" t="n">
-        <v>6715923.544456638</v>
+        <v>6715994</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104424281</v>
+        <v>104424279</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406933.2178725838</v>
+        <v>406936</v>
       </c>
       <c r="R4" t="n">
-        <v>6715988.336118942</v>
+        <v>6715986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104424297</v>
+        <v>104424282</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406781.2479692398</v>
+        <v>406923</v>
       </c>
       <c r="R5" t="n">
-        <v>6715731.57477543</v>
+        <v>6715980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104424282</v>
+        <v>104424285</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406923.1557675265</v>
+        <v>406907</v>
       </c>
       <c r="R6" t="n">
-        <v>6715980.234520668</v>
+        <v>6715989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104424294</v>
+        <v>104424289</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406806.609041239</v>
+        <v>406872</v>
       </c>
       <c r="R7" t="n">
-        <v>6715797.814399661</v>
+        <v>6715933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104424278</v>
+        <v>104424291</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406942.7368619765</v>
+        <v>406871</v>
       </c>
       <c r="R8" t="n">
-        <v>6715994.48436602</v>
+        <v>6715923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104424815</v>
+        <v>104424292</v>
       </c>
       <c r="B9" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406957.2029599793</v>
+        <v>406838</v>
       </c>
       <c r="R9" t="n">
-        <v>6715791.465255608</v>
+        <v>6715874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,31 +1439,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104424813</v>
+        <v>104424294</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1607,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406988.390973739</v>
+        <v>406806</v>
       </c>
       <c r="R10" t="n">
-        <v>6715950.023528217</v>
+        <v>6715798</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,49 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104424287</v>
+        <v>104424295</v>
       </c>
       <c r="B11" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406873.6895342277</v>
+        <v>406785</v>
       </c>
       <c r="R11" t="n">
-        <v>6715934.29444168</v>
+        <v>6715778</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104424292</v>
+        <v>104424297</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406838.6363234204</v>
+        <v>406781</v>
       </c>
       <c r="R12" t="n">
-        <v>6715874.209775616</v>
+        <v>6715731</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,19 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104424295</v>
+        <v>104424813</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1943,14 +1773,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406784.43751606</v>
+        <v>406989</v>
       </c>
       <c r="R13" t="n">
-        <v>6715778.712650876</v>
+        <v>6715950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,31 +1827,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104424289</v>
+        <v>104424817</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2055,14 +1870,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406871.6694409045</v>
+        <v>406965</v>
       </c>
       <c r="R14" t="n">
-        <v>6715932.379212972</v>
+        <v>6715814</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,62 +1924,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104424296</v>
+        <v>128186215</v>
       </c>
       <c r="B15" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406778.7039413999</v>
+        <v>406750</v>
       </c>
       <c r="R15" t="n">
-        <v>6715766.56399907</v>
+        <v>6715629</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,22 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,62 +2021,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104424293</v>
+        <v>128186216</v>
       </c>
       <c r="B16" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406800.1515373869</v>
+        <v>406821</v>
       </c>
       <c r="R16" t="n">
-        <v>6715833.887861075</v>
+        <v>6715709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,22 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,27 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104424290</v>
+        <v>104424816</v>
       </c>
       <c r="B17" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,34 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Häståsen, Åskakskölen, Vrm</t>
+          <t>Häståsen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406868.6646936154</v>
+        <v>406957</v>
       </c>
       <c r="R17" t="n">
-        <v>6715930.489422228</v>
+        <v>6715792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,27 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104424279</v>
+        <v>104424290</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406936.1210233149</v>
+        <v>406869</v>
       </c>
       <c r="R18" t="n">
-        <v>6715986.293785494</v>
+        <v>6715930</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104424817</v>
+        <v>104424293</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,34 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406965.1716464885</v>
+        <v>406800</v>
       </c>
       <c r="R19" t="n">
-        <v>6715813.885654526</v>
+        <v>6715834</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2392,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,27 +2409,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104424816</v>
+        <v>104424281</v>
       </c>
       <c r="B20" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,34 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Häståsen, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406957.2029599793</v>
+        <v>406933</v>
       </c>
       <c r="R20" t="n">
-        <v>6715791.465255608</v>
+        <v>6715988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2489,9 @@
           <t>2022-10-31</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,22 +2506,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128186215</v>
+        <v>104424286</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,34 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406750</v>
+        <v>406884</v>
       </c>
       <c r="R21" t="n">
-        <v>6715629</v>
+        <v>6715972</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2868,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,22 +2603,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128186216</v>
+        <v>104424287</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2626,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Häståsen, Åskakskölen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406821</v>
+        <v>406873</v>
       </c>
       <c r="R22" t="n">
-        <v>6715709</v>
+        <v>6715935</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,15 +2700,209 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104424814</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Häståsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>406962</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6715888</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104424815</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Häståsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>406957</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6715792</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36543-2025 artfynd.xlsx
+++ b/artfynd/A 36543-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424278</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424279</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424282</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424289</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424291</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424292</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424294</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424295</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424297</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424817</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128186215</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128186216</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424816</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424290</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424293</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424281</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424286</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424287</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424814</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,8 +3018,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104424815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>